--- a/excel-files/atlas-tactics.xlsx
+++ b/excel-files/atlas-tactics.xlsx
@@ -355,16 +355,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -387,7 +379,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -395,35 +387,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -723,25 +697,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -758,7 +732,7 @@
       <c r="D2" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
@@ -781,7 +755,7 @@
       <c r="D3" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F3" t="s">
@@ -804,7 +778,7 @@
       <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F4" t="s">
@@ -827,7 +801,7 @@
       <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F5" t="s">
@@ -850,7 +824,7 @@
       <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="F6" t="s">
@@ -873,7 +847,7 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F7" t="s">
@@ -896,7 +870,7 @@
       <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F8" t="s">
@@ -919,7 +893,7 @@
       <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F9" t="s">
@@ -942,7 +916,7 @@
       <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F10" t="s">
@@ -965,7 +939,7 @@
       <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F11" t="s">
@@ -988,7 +962,7 @@
       <c r="D12" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F12" t="s">
@@ -1011,7 +985,7 @@
       <c r="D13" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F13" t="s">
@@ -1034,7 +1008,7 @@
       <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>83</v>
       </c>
       <c r="F14" t="s">
@@ -1057,7 +1031,7 @@
       <c r="D15" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F15" t="s">
@@ -1080,7 +1054,7 @@
       <c r="D16" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F16" t="s">
@@ -1103,7 +1077,7 @@
       <c r="D17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F17" t="s">

--- a/excel-files/atlas-tactics.xlsx
+++ b/excel-files/atlas-tactics.xlsx
@@ -355,8 +355,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -379,7 +387,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -387,17 +395,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -697,25 +723,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -732,7 +758,7 @@
       <c r="D2" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
@@ -755,7 +781,7 @@
       <c r="D3" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F3" t="s">
@@ -778,7 +804,7 @@
       <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F4" t="s">
@@ -801,7 +827,7 @@
       <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F5" t="s">
@@ -824,7 +850,7 @@
       <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F6" t="s">
@@ -847,7 +873,7 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F7" t="s">
@@ -870,7 +896,7 @@
       <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F8" t="s">
@@ -893,7 +919,7 @@
       <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F9" t="s">
@@ -916,7 +942,7 @@
       <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F10" t="s">
@@ -939,7 +965,7 @@
       <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F11" t="s">
@@ -962,7 +988,7 @@
       <c r="D12" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F12" t="s">
@@ -985,7 +1011,7 @@
       <c r="D13" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F13" t="s">
@@ -1008,7 +1034,7 @@
       <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F14" t="s">
@@ -1031,7 +1057,7 @@
       <c r="D15" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>84</v>
       </c>
       <c r="F15" t="s">
@@ -1054,7 +1080,7 @@
       <c r="D16" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F16" t="s">
@@ -1077,7 +1103,7 @@
       <c r="D17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F17" t="s">
